--- a/prompts/prompts_2026_SurkovaOlga.xlsx
+++ b/prompts/prompts_2026_SurkovaOlga.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\savelij\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{284C8103-4190-49D9-9E71-1CED9145542B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1541BEF1-B6E5-40CA-966F-125C9A15E7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
   <si>
     <t>Platform</t>
   </si>
@@ -1556,9 +1556,6 @@
 Нужен только код построения исправленного графика.
 Код должен быть понятным для начинающего студента, с комментариями.</t>
   </si>
-  <si>
-    <t>4 Анализ и визуализация</t>
-  </si>
 </sst>
 </file>
 
@@ -1616,6 +1613,8 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2140,7 +2139,7 @@
         <v>46181.463888888888</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1">
         <v>8</v>
